--- a/output/pdf_financials_xlsx/FINV.P.xlsx
+++ b/output/pdf_financials_xlsx/FINV.P.xlsx
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.181776</v>
+        <v>-0.181776</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.181776</v>
+        <v>-0.181776</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -965,16 +965,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.181776</v>
+        <v>-0.181776</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>9.088800000000001</v>
+        <v>-9.088800000000001</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.181776</v>
+        <v>-0.181776</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.181776</v>
+        <v>-0.181776</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -2685,16 +2685,16 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.111416</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.111416</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.111416</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.111416</v>
       </c>
     </row>
     <row r="93">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.181776</v>
@@ -4091,7 +4091,11 @@
           <t>Share-based payment reserves 5 111,416</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4663,7 +4667,11 @@
           <t>Share-based payment reserves 4</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6480,7 +6488,7 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7097,10 +7105,10 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.064384</v>
+        <v>-0.064384</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.031744</v>
+        <v>-0.031744</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7488,10 +7496,10 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.181776</v>
+        <v>-0.181776</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.064384</v>
+        <v>-0.064384</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7983,7 +7991,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.019925</v>
+        <v>-0.019925</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FINV.P.xlsx
+++ b/output/pdf_financials_xlsx/FINV.P.xlsx
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.019668</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>-0.031744</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.031744</v>
+        <v>-0.012076</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>-0.031744</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.031744</v>
+        <v>-0.012076</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.471137</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.397238</v>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.471137</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.397238</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">

--- a/output/pdf_financials_xlsx/FINV.P.xlsx
+++ b/output/pdf_financials_xlsx/FINV.P.xlsx
@@ -1237,10 +1237,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.349653</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.471137</v>
@@ -1261,10 +1259,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1285,10 +1281,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.349653</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.471137</v>
@@ -1309,10 +1303,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1333,10 +1325,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1357,10 +1347,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1381,10 +1369,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1405,10 +1391,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1429,10 +1413,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1453,10 +1435,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1477,10 +1457,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1501,10 +1479,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1525,10 +1501,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1549,10 +1523,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1573,10 +1545,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -1629,10 +1599,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1653,10 +1621,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1677,10 +1643,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1701,10 +1665,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1725,10 +1687,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1781,10 +1741,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1805,10 +1763,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1829,10 +1785,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -1853,10 +1807,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1877,10 +1829,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1901,10 +1851,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -1957,10 +1905,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0.364653</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>0.471137</v>
@@ -1981,10 +1927,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0.008578000000000001</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0.013872</v>
@@ -2005,10 +1949,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -2029,10 +1971,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -2053,10 +1993,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.006</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0.008</v>
@@ -2077,10 +2015,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.014578</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.021872</v>
@@ -2101,10 +2037,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -2125,10 +2059,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -2149,10 +2081,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -2173,10 +2103,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -2197,10 +2125,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -2221,10 +2147,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -2245,10 +2169,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -2301,10 +2223,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2325,10 +2245,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -2349,10 +2267,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2405,10 +2321,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -2429,10 +2343,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -2453,10 +2365,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -2477,10 +2387,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -2501,10 +2409,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -2557,10 +2463,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.014578</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.021872</v>
@@ -2581,10 +2485,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.37</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.53955</v>
@@ -2605,10 +2507,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -2655,10 +2555,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2679,10 +2577,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.111416</v>
@@ -2703,10 +2599,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2727,10 +2621,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.350075</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>0.449265</v>
@@ -2751,10 +2643,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2775,10 +2665,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.350075</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>0.449265</v>
@@ -2799,10 +2687,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.960022267744952</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>0.9535761360283739</v>
@@ -2957,7 +2843,7 @@
         <v>0.007294</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>-0.009514999999999999</v>
+        <v>0.003685</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.003685</v>
@@ -3005,7 +2891,7 @@
         <v>0.007294</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.009514999999999999</v>
+        <v>0.003685</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.003685</v>
@@ -3601,7 +3487,7 @@
         <v>0.349653</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.471137</v>
+        <v>0.397238</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.397238</v>
@@ -3675,7 +3561,7 @@
         <v>0.471137</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.397238</v>
+        <v>0.369179</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>0.369179</v>
@@ -3749,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4268,10 +4154,8 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4935,31 +4819,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Current assets</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>November 30, 2024 November</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash 471,137</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.349653</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>3e-05</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4970,37 +4864,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>-0.181776</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-0.064384</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>-0.031744</v>
+          <t>Deferred financing fees 5 -</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -5011,37 +4905,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Total assets 471,137</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.007294</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>-0.009514999999999999</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0.003685</v>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.364653</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -5052,35 +4950,41 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net cash and cash equivalents used in operating activities</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable 13,872</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.008578000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
-        <v>-0.07389900000000001</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>-0.028059</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -5091,35 +4995,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents for the year</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accrued liabilities 8,000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CurrentAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.006</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n">
-        <v>-0.07389900000000001</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>-0.028059</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -5130,39 +5040,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents - beginning of the year</t>
+          <t>Total liabilities 21,872</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.014578</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>0.471137</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0.397238</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -5173,39 +5085,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents - end of the year</t>
+          <t>Share capital 6 539,550</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>0.397238</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>0.369179</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -5216,20 +5130,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Share based payments reserve 6 111,416</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -5240,11 +5158,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n">
-        <v>0.022238</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0.023212</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -5255,35 +5177,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash equivalents</t>
+          <t>Deficit (201,701)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="5" t="n">
+        <v>-0.019925</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>0.345967</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -5294,35 +5218,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total shareholders’ equity 449,265</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.350075</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>0.397238</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0.369179</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -5333,26 +5263,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SHAREHOLDERS’ EQUITY</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>November 30, 2023 November</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>3e-05</v>
+          <t>Total liabilities and shareholders’ equity 471,137</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.364653</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5368,31 +5308,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Add non-cash items</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.09246600000000001</v>
+          <t>Subsequent event (Note</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5418,29 +5354,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Net loss (37,094)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>-0.08201600000000001</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.07389900000000001</v>
+        <v>-0.031744</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5461,17 +5395,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Proceeds from Initial public offering, net of share issuance costs</t>
+          <t>Accounts payable and accrued liabilities (2,135)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5479,13 +5413,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.2035</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.003685</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5506,31 +5440,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Net cash and cash equivalents used in operating activities (39,229)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>0.2035</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.028059</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5551,29 +5481,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Change in cash for the year</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents for the year (39,229)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.121484</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.07389900000000001</v>
+        <v>-0.028059</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5594,12 +5522,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash - beginning of year</t>
+          <t>Cash and cash equivalents - beginning of the year 369,179</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5612,11 +5540,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.349653</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.471137</v>
+        <v>0.397238</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5637,12 +5567,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash - end of year</t>
+          <t>Cash and cash equivalents - end of the year 329,950</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5655,11 +5585,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>0.471137</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.397238</v>
+        <v>0.369179</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5680,27 +5612,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Net loss (181,776)</t>
+          <t>Cash 24,231</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>-0.019925</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="5" t="n">
+        <v>0.023212</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5721,19 +5653,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Add non-cash items</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share based compensation 92,466</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Cash equivalents 305,719</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -5744,10 +5672,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="5" t="n">
+        <v>0.345967</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5773,26 +5699,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 7,294</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0.014578</v>
+          <t>Cash and cash equivalents 329,950</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" s="5" t="n">
+        <v>0.369179</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5811,38 +5733,28 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital total</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>-0.005347</v>
+          <t>November 30, 2024 November</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G50" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5858,17 +5770,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Proceeds from Initial public offering, net of share issuance costs 203,500</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5876,20 +5788,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="5" t="n">
+        <v>-0.181776</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.064384</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>-0.031744</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5905,32 +5811,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Proceeds from private placement -</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.007294</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.009514999999999999</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.003685</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5946,32 +5852,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Payment of deferred financing fees -</t>
+          <t>Net cash and cash equivalents used in operating activities</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>-0.015</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G53" s="5" t="n">
+        <v>-0.07389900000000001</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.028059</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5987,36 +5891,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Financing Activities total</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0.355</v>
+          <t>Change in cash and cash equivalents for the year</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" s="5" t="n">
+        <v>-0.07389900000000001</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>-0.028059</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6032,36 +5930,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Change in cash for the year 121,484</t>
+          <t>Cash and cash equivalents - beginning of the year</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0.349653</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G55" s="5" t="n">
+        <v>0.471137</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.397238</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6077,15 +5973,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cash - beginning 349,653</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Cash and cash equivalents - end of the year</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -6096,15 +5996,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G56" s="5" t="n">
+        <v>0.397238</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.369179</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6120,32 +6016,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cash - ending 471,137</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>0.349653</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G57" s="5" t="n">
+        <v>0.022238</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.023212</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6156,17 +6050,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Accounting and audit 20,852</t>
+          <t>Cash equivalents</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -6181,12 +6075,10 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.027525</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.375</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.345967</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6197,24 +6089,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bank charges and interest expense 436</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6226,12 +6114,10 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.000637</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.397238</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.369179</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6242,36 +6128,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>General and administrative expenses 886</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>November 30, 2023 November</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F60" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.00043</v>
+        <v>3e-05</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -6287,32 +6163,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Add non-cash items</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Legal expenses 8,190</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.006682</v>
+      <c r="F61" s="5" t="n">
+        <v>0.09246600000000001</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -6328,22 +6208,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Listing and filing fees 16,136</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6351,13 +6231,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>-0.08201600000000001</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.016138</v>
+        <v>-0.07389900000000001</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6373,22 +6251,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Loss before other items 46,500</t>
+          <t>Proceeds from Initial public offering, net of share issuance costs</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6396,13 +6274,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.051412</v>
+      <c r="F63" s="5" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6418,32 +6296,36 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Interest income (9,406)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>-0.019668</v>
+      <c r="F64" s="5" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -6459,22 +6341,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss 37,094</t>
+          <t>Change in cash for the year</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6482,13 +6364,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="5" t="n">
+        <v>0.121484</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.031744</v>
+        <v>-0.07389900000000001</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -6504,32 +6384,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Basic and diluted 0.00</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Cash - beginning of year</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="5" t="n">
+        <v>0.349653</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>0.471137</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -6545,32 +6427,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2023 9,900,000 539,550 111,416 (266,085)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Cash - end of year</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>0.471137</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.384881</v>
+        <v>0.397238</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -6586,32 +6470,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - (31,744)</t>
+          <t>Net loss (181,776)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="5" t="n">
+        <v>-0.019925</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>-0.031744</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6627,20 +6511,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Add non-cash items</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2024 9,900,000 539,550 111,416 (297,829)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Share based compensation 92,466</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6651,8 +6539,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>0.353137</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -6668,32 +6558,36 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - (37,094)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities 7,294</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.014578</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G70" s="5" t="n">
-        <v>-0.037094</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -6709,32 +6603,36 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2025 9,900,000 539,550 111,416 (334,923)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Changes in non-cash working capital total</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.005347</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n">
-        <v>0.316043</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -6750,16 +6648,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>November 30, 2024 November</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Proceeds from Initial public offering, net of share issuance costs 203,500</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -6770,11 +6676,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G72" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>3e-05</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6785,33 +6695,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accounting and audit</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0.020549</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0.026205</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>0.027525</v>
+          <t>Proceeds from private placement -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6822,37 +6740,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bank charges and interest expense</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>0.000492</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>0.000731</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>0.000637</v>
+          <t>Payment of deferred financing fees -</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6863,28 +6781,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing Activities total</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0.355</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6896,8 +6812,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>0.00043</v>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6908,33 +6826,41 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Legal expenses</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.036791</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.020591</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>0.006682</v>
+          <t>Change in cash for the year 121,484</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.349653</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6945,24 +6871,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>--</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Cash - beginning 349,653</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6973,11 +6895,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" s="5" t="n">
-        <v>0.016857</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.016138</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6988,39 +6914,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>--</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash - ending 471,137</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0.349653</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G78" s="5" t="n">
-        <v>0.064384</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>0.051412</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7036,19 +6960,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Accounting and audit 20,852</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -7059,13 +6979,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>-0.019668</v>
+      <c r="G79" s="5" t="n">
+        <v>0.027525</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7081,17 +7001,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Bank charges and interest expense 436</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7105,10 +7025,12 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.064384</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>-0.031744</v>
+        <v>0.000637</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7124,17 +7046,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>General and administrative expenses 886</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7142,14 +7064,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>2e-08</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0</v>
+        <v>0.00043</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7165,19 +7091,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Legal expenses 8,190</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7189,10 +7111,12 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>9.9</v>
+        <v>0.006682</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7208,28 +7132,36 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2022 9,900,000 539,550 111,416</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Listing and filing fees 16,136</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0.449265</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.449265</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>-0.201701</v>
+        <v>0.016138</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -7245,17 +7177,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - -</t>
+          <t>Loss before other items 46,500</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7263,14 +7195,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.181776</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.064384</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>-0.064384</v>
+        <v>0.051412</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7286,12 +7222,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2023 9,900,000 539,550 111,416</t>
+          <t>Interest income (9,406)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -7300,14 +7236,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>0.384881</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.384881</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>-0.266085</v>
+        <v>-0.019668</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7323,15 +7263,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2024 9,900,000 539,550 111,416</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Net loss and comprehensive loss 37,094</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7343,10 +7287,12 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.353137</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>-0.297829</v>
+        <v>-0.031744</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7360,10 +7306,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>November 30, 2023 November</t>
+          <t>Basic and diluted 0.00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7372,11 +7322,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>0.002022</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -7397,12 +7349,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Listing fees</t>
+          <t>Balance, November 30, 2023 9,900,000 539,550 111,416 (266,085)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -7411,11 +7363,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>0.031478</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.016857</v>
+        <v>0.384881</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7436,12 +7390,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Share-based compensation 4,5</t>
+          <t>Net loss and comprehensive loss - - - (31,744)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7450,13 +7404,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>0.09246600000000001</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.031744</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7477,29 +7431,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, November 30, 2024 9,900,000 539,550 111,416 (297,829)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>-0.181776</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.064384</v>
+        <v>0.353137</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7520,12 +7472,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Weighted number of common shares outstanding</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Net loss and comprehensive loss - - - (37,094)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7534,11 +7486,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>7.942482</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>9.9</v>
+        <v>-0.037094</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7564,7 +7518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2021 7,400,000 370,000 -</t>
+          <t>Balance, November 30, 2025 9,900,000 539,550 111,416 (334,923)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7573,11 +7527,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0.350075</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.019925</v>
+        <v>0.316043</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -7596,14 +7552,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Initial Public Offering (“IPO”) (Note 4) 2,500,000 250,000 -</t>
+          <t>November 30, 2024 November</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7612,18 +7564,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7639,12 +7589,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 4) (61,500) -</t>
+          <t>Accounting and audit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7654,17 +7604,13 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.0615</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020549</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.026205</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.027525</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7680,34 +7626,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Warrants issued to Agents in conjunction with IPO (Note 4) - (18,950) 18,950</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Bank charges and interest expense</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F95" s="5" t="n">
+        <v>0.000492</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.000731</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>0.000637</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7723,32 +7667,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 4) - - 92,466</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>0.09246600000000001</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H96" s="5" t="n">
+        <v>0.00043</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7769,27 +7717,23 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Accounting and audit 20,549</t>
+          <t>Legal expenses</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>0.007906</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.036791</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.020591</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.006682</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7810,31 +7754,29 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bank charges and interest expense 492</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0.000252</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G98" s="5" t="n">
+        <v>0.016857</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>0.016138</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7855,27 +7797,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Legal expenses 36,791</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>0.011767</v>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G99" s="5" t="n">
+        <v>0.064384</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.051412</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7891,15 +7835,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Listing fees 31,478</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -7915,10 +7863,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H100" s="5" t="n">
+        <v>-0.019668</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7934,15 +7880,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share based compensation 6 92,466</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -7953,15 +7903,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="5" t="n">
+        <v>-0.064384</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-0.031744</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7977,36 +7923,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year 181,776</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>-0.019925</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8022,32 +7964,34 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Net loss per share-</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Basic and diluted 0.02</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>1e-08</v>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>9.9</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -8063,34 +8007,889 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Balance, November 30, 2022 9,900,000 539,550 111,416</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.449265</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.449265</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-0.201701</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>-0.181776</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>-0.064384</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>-0.064384</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Balance, November 30, 2023 9,900,000 539,550 111,416</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.384881</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.384881</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>-0.266085</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Balance, November 30, 2024 9,900,000 539,550 111,416</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.353137</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>-0.297829</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>November 30, 2023 November</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0.031478</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.016857</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Share-based compensation 4,5</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.09246600000000001</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-0.181776</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-0.064384</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Weighted number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>7.942482</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Balance, November 30, 2021 7,400,000 370,000 -</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0.350075</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-0.019925</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Initial Public Offering (“IPO”) (Note 4) 2,500,000 250,000 -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Share issuance costs (Note 4) (61,500) -</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>-0.0615</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Warrants issued to Agents in conjunction with IPO (Note 4) - (18,950) 18,950</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 4) - - 92,466</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.09246600000000001</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Accounting and audit 20,549</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>0.007906</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Bank charges and interest expense 492</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.000252</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Legal expenses 36,791</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>0.011767</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Listing fees 31,478</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Share based compensation 6 92,466</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year 181,776</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>-0.019925</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Net loss per share-</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Basic and diluted 0.02</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>Weighted number of common shares outstanding-</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Basic and diluted 7,942,482</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
         <v>1.409524</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
